--- a/resources/HEARTH_Festival_Submission_Tracker.xlsx
+++ b/resources/HEARTH_Festival_Submission_Tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="103">
   <si>
     <t xml:space="preserve">HEARTH  ·  Festival Submission Tracker</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t xml:space="preserve">ADD YOUR SUBMISSIONS BELOW — One row per festival. Update Status as responses arrive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Festival Status &amp; Tier Reference</t>
@@ -338,7 +341,7 @@
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +414,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -587,11 +598,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -648,11 +663,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -660,7 +679,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -668,7 +687,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -676,7 +695,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -684,7 +703,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -692,7 +711,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -700,11 +719,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -712,15 +731,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,7 +769,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF888898"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FFB84A00"/>
       <rgbColor rgb="FFFDEEDE"/>
@@ -976,768 +995,783 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <f aca="false">COUNTIF(I11:I1000,"&lt;&gt;""")</f>
         <v>990</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <f aca="false">COUNTIF(I11:I1000,"Accepted")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <f aca="false">COUNTIF(I11:I1000,"Rejected")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <f aca="false">COUNTIF(I11:I1000,"Submitted")+COUNTIF(I11:I1000,"Awaiting Decision")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <f aca="false">SUM(E11:E1000)</f>
         <v>455</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9" t="s">
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9" t="s">
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9" t="s">
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9" t="s">
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9" t="s">
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9" t="s">
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9" t="s">
+      <c r="F19" s="10"/>
+      <c r="G19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9" t="s">
+      <c r="F20" s="10"/>
+      <c r="G20" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9" t="s">
+      <c r="F21" s="10"/>
+      <c r="G21" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="12"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="12"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="12"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="12"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="12"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="12"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="12"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="12"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="12"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="12"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="12"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="12"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B23:J23"/>
+    <mergeCell ref="A55:J55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1757,197 +1791,197 @@
   <dimension ref="B1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="15"/>
+      <c r="B2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="16"/>
+      <c r="B4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>69</v>
       </c>
+      <c r="C5" s="20" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>71</v>
       </c>
+      <c r="C6" s="22" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>73</v>
       </c>
+      <c r="C7" s="24" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="B8" s="25" t="s">
         <v>75</v>
       </c>
+      <c r="C8" s="26" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>76</v>
+      <c r="C9" s="28" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="29" t="s">
         <v>78</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="29"/>
+      <c r="B12" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>80</v>
+      <c r="C13" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="32" t="s">
-        <v>81</v>
+      <c r="C14" s="34" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="31" t="s">
-        <v>82</v>
+      <c r="C15" s="33" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="32" t="s">
-        <v>83</v>
+      <c r="C16" s="34" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="33"/>
+      <c r="B18" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="32" t="s">
         <v>86</v>
       </c>
+      <c r="C19" s="33" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="32" t="s">
+      <c r="B20" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="C20" s="34" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="32" t="s">
         <v>90</v>
       </c>
+      <c r="C21" s="33" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="32" t="s">
+      <c r="B22" s="3" t="s">
         <v>92</v>
       </c>
+      <c r="C22" s="34" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="31" t="s">
+      <c r="B23" s="32" t="s">
         <v>94</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="16"/>
+      <c r="B25" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="32" t="s">
-        <v>96</v>
+      <c r="C26" s="34" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="31" t="s">
+      <c r="B27" s="32" t="s">
         <v>98</v>
       </c>
+      <c r="C27" s="33" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="32" t="s">
-        <v>99</v>
+      <c r="C28" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="31" t="s">
+      <c r="B29" s="32" t="s">
         <v>101</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/resources/HEARTH_Festival_Submission_Tracker.xlsx
+++ b/resources/HEARTH_Festival_Submission_Tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
   <si>
     <t xml:space="preserve">HEARTH  ·  Festival Submission Tracker</t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t xml:space="preserve">ADD YOUR SUBMISSIONS BELOW — One row per festival. Update Status as responses arrive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Festival Status &amp; Tier Reference</t>
@@ -341,7 +338,7 @@
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,14 +411,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -598,15 +587,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -663,15 +648,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -679,7 +660,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -687,7 +668,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -695,7 +676,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -703,7 +684,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -711,7 +692,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -719,11 +700,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -731,15 +712,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -769,7 +750,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF888898"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FFB84A00"/>
       <rgbColor rgb="FFFDEEDE"/>
@@ -995,783 +976,768 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="B1:J53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <f aca="false">COUNTIF(I11:I1000,"&lt;&gt;""")</f>
         <v>990</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <f aca="false">COUNTIF(I11:I1000,"Accepted")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="5" t="n">
         <f aca="false">COUNTIF(I11:I1000,"Rejected")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="5" t="n">
         <f aca="false">COUNTIF(I11:I1000,"Submitted")+COUNTIF(I11:I1000,"Awaiting Decision")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6" t="n">
         <f aca="false">SUM(E11:E1000)</f>
         <v>455</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="9"/>
+      <c r="G11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="9"/>
+      <c r="G13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10" t="s">
+      <c r="F14" s="9"/>
+      <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="9"/>
+      <c r="G15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10" t="s">
+      <c r="F18" s="9"/>
+      <c r="G18" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10" t="s">
+      <c r="F19" s="9"/>
+      <c r="G19" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10" t="s">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="13"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="13"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="13"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="13"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="13"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="13"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="13"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="13"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="13"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="13"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="13"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="13"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="13"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="13"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="13"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="13"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="13"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="13"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="13"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="13"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="13"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="13"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="13"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="13"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="13"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="13"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="13"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="13"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="13"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="13"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="13"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="13"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="13"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="13"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="13"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="13"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="13"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="13"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="13"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="13"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="13"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="13"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B23:J23"/>
-    <mergeCell ref="A55:J55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1791,197 +1757,197 @@
   <dimension ref="B1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="17"/>
+      <c r="B2" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="18"/>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="20" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="22" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="21" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="24" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="23" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="26" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="28" t="s">
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="27" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
+      <c r="C10" s="28" t="s">
         <v>78</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="29"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="31"/>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="33" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="34" t="s">
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="31" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="33" t="s">
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="33"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="35"/>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
+      <c r="C19" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="33" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="34" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="30" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="C21" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="33" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="34" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="30" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="32" t="s">
+      <c r="C23" s="31" t="s">
         <v>94</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="34" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="30" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="32" t="s">
+      <c r="C27" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="33" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="32" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="34" t="s">
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="30" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="32" t="s">
+      <c r="C29" s="31" t="s">
         <v>101</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
